--- a/Templates/Template_SA-5_Accordo_di_scambio_tra_domini_FE.xlsx
+++ b/Templates/Template_SA-5_Accordo_di_scambio_tra_domini_FE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA-5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SA-5'!$A$1:$I$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SA-5'!$A$1:$L$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -118,11 +118,55 @@
         <color rgb="008EA9DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="008EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="008EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="008EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="008EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="008EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="008EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,7 +189,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -526,18 +571,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -547,28 +595,28 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Template ARCADIA per i team di sviluppo · v1.0 · 28/09/2026 · Baseline delle specifiche: SUBSET-026 v3.6.0 (B3R2) · Chi compila: responsabili dei team dei due/k domini · Livello: SA, LA · Ordine di compilazione: 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17" customHeight="1">
+          <t>Template ARCADIA per i team di sviluppo · v1.1 · 30/10/2026 · Baseline delle specifiche: SUBSET-026 v3.6.0 (B3R2) · Chi compila: responsabili dei team dei due/k domini · Livello: SA, LA · Ordine di compilazione: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Scopo. Concordare ogni scambio tra funzioni di domini diversi.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
+    <row r="4" ht="39" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Come si compila. Uno scambio si registra una volta e si riusa in tutte le chain. Natura: FLOW (valore sempre disponibile), EVENT (fatto accaduto), OPERATION (richiesta eseguita da un altro dominio).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
+          <t>Come si compila. Uno scambio si registra una volta e si riusa in tutte le chain. Natura: FLOW (valore sempre disponibile), EVENT (fatto accaduto), OPERATION (richiesta eseguita da un altro dominio). In ATLAS è la scheda dello scambio funzionale (SA-5); le chain che lo usano sono calcolate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Legenda: le celle bianche vanno compilate; il testo grigio in corsivo è guida o esempio del template e va sostituito. Le celle «Stato» e le colonne a valori fissi propongono un elenco a tendina.</t>
@@ -597,18 +645,21 @@
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Versione</t>
         </is>
       </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>es. 0.1</t>
         </is>
       </c>
-      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="9" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -616,28 +667,31 @@
           <t>Autore</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Revisore</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="8" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>gg/mm/aaaa</t>
         </is>
       </c>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="31" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Stato</t>
@@ -659,283 +713,361 @@
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Rif. Capella / DOORS</t>
         </is>
       </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="8" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="9" t="n"/>
+    </row>
+    <row r="11" ht="41" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>ID scambio</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Produttore (funzione, dominio)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Utilizzatore (funzione, dominio)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Dato di interfaccia</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Natura</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Condizione di produzione</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Clausole</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Chain che lo usano</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Accordo del produttore</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Accordo dell'utilizzatore</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="41" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>FE-DF02-DF06-01</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Determinare velocità, accelerazione e standstill (DF02)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Movimento del treno</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Determinare velocità e standstill (DF02)</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Supervisionare lo standstill (DF06)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Movimento del treno</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>EI-movimento_treno</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>FLOW</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Sempre</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>3.14.4.2</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>FC-Movimenti-Indesiderati</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Concordato</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Calcolato da ATLAS</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Referente DF02, data</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Referente DF06, data</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Proposto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Checklist di compilazione di SA-5</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -952,9 +1084,12 @@
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="8" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -971,9 +1106,12 @@
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -990,48 +1128,178 @@
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
+  <mergeCells count="15">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="49">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bozza,In revisione,Approvato"</formula1>
     </dataValidation>
-    <dataValidation sqref="E12:E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FLOW,EVENT,OPERATION"</formula1>
-    </dataValidation>
-    <dataValidation sqref="A30 A31 A32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"☐,☑"</formula1>
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FLOW,EVENT,OPERATION"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sempre,A ogni variazione,Su evento,Su richiesta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Proposto,Concordato,Approvato"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 Informazione ad uso interno - Internal use information&amp;R&amp;8 &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>